--- a/pharma_config_ckd.xlsx
+++ b/pharma_config_ckd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Neodocs\Data\ppt_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA72BE3-F101-475D-8434-5128892FA516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95AAA4F-8E3C-498D-96B6-37C7E3028820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,12 +87,6 @@
     <t>J1W82P4TzIDDGCXXfHCE</t>
   </si>
   <si>
-    <t>linadapa</t>
-  </si>
-  <si>
-    <t>benitowa</t>
-  </si>
-  <si>
     <t>4fedd099-4819-4e96-890d-9d3f217a0943</t>
   </si>
   <si>
@@ -124,6 +118,12 @@
   </si>
   <si>
     <t>template1gennovaACR.pptx</t>
+  </si>
+  <si>
+    <t>Akumentis (Benitowa)</t>
+  </si>
+  <si>
+    <t>Akumentis (Linadapa)</t>
   </si>
 </sst>
 </file>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
@@ -566,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -574,11 +574,11 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
       <c r="C7">
         <v>10</v>
       </c>
@@ -586,7 +586,7 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -594,11 +594,11 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
       <c r="C8">
         <v>10</v>
       </c>
@@ -606,7 +606,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -614,10 +614,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -626,7 +626,7 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -634,19 +634,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10">
-        <v>10</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
